--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_software_system_application.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,32 +587,35 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
+      <c r="E2">
+        <v>-0.0298</v>
+      </c>
       <c r="G2">
-        <v>-0.3810927046830201</v>
+        <v>-0.9586079077429984</v>
       </c>
       <c r="H2">
-        <v>-0.6068811723478815</v>
+        <v>-1.209843492586491</v>
       </c>
       <c r="I2">
-        <v>-0.7797688568333877</v>
+        <v>-1.036449752883031</v>
       </c>
       <c r="J2">
-        <v>-0.7797688568333877</v>
+        <v>-1.036449752883031</v>
       </c>
       <c r="K2">
-        <v>-4.643</v>
+        <v>-10</v>
       </c>
       <c r="L2">
-        <v>-0.3697833705001593</v>
+        <v>-2.059308072487644</v>
       </c>
       <c r="M2">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="N2">
-        <v>0.04854368932038835</v>
+        <v>0.3212290502793296</v>
       </c>
       <c r="O2">
-        <v>-0.2584535860435064</v>
+        <v>-0.23</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +627,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>10</v>
+        <v>4.536</v>
       </c>
       <c r="V2">
-        <v>0.4045307443365696</v>
+        <v>0.6335195530726258</v>
       </c>
       <c r="W2">
-        <v>-0.5623770999322414</v>
+        <v>-1.027272727272727</v>
       </c>
       <c r="X2">
-        <v>0.1970979437463645</v>
+        <v>0.4250715120403666</v>
       </c>
       <c r="Y2">
-        <v>-0.7594750436786059</v>
+        <v>-1.452344239313094</v>
       </c>
       <c r="Z2">
-        <v>0.5689457269726098</v>
-      </c>
-      <c r="AA2">
-        <v>-1.203084402683148</v>
+        <v>0.3638543383785403</v>
       </c>
       <c r="AB2">
-        <v>0.1497191431319402</v>
-      </c>
-      <c r="AC2">
-        <v>-1.352803545815088</v>
+        <v>0.2644821022749581</v>
       </c>
       <c r="AD2">
-        <v>7.538</v>
+        <v>5.15</v>
       </c>
       <c r="AE2">
-        <v>0.1388888320000831</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.676888832000084</v>
+        <v>5.15</v>
       </c>
       <c r="AG2">
-        <v>-2.323111167999916</v>
+        <v>0.6139999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2369637674719316</v>
+        <v>0.4183590576766856</v>
       </c>
       <c r="AI2">
-        <v>0.2669582539630433</v>
+        <v>0.2178510998307953</v>
       </c>
       <c r="AJ2">
-        <v>-0.1037247264754342</v>
+        <v>0.07898121944944686</v>
       </c>
       <c r="AK2">
-        <v>-0.1238537578810291</v>
+        <v>0.03213986599664991</v>
       </c>
       <c r="AL2">
-        <v>2.473</v>
+        <v>1.096</v>
       </c>
       <c r="AM2">
-        <v>2.473</v>
+        <v>-0.004000000000000004</v>
       </c>
       <c r="AN2">
-        <v>-2.91831204026326</v>
+        <v>-1.221247332226701</v>
       </c>
       <c r="AO2">
-        <v>-3.970885564092196</v>
+        <v>-4.592153284671532</v>
       </c>
       <c r="AP2">
-        <v>0.8993848888888564</v>
+        <v>-0.1456011382499407</v>
       </c>
       <c r="AQ2">
-        <v>-3.970885564092196</v>
+        <v>1258.249999999999</v>
       </c>
     </row>
     <row r="3">
@@ -715,32 +712,35 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
+      <c r="E3">
+        <v>-0.0298</v>
+      </c>
       <c r="G3">
-        <v>64.65909090909091</v>
+        <v>-10.18292682926829</v>
       </c>
       <c r="H3">
-        <v>70.22727272727273</v>
+        <v>-10.18292682926829</v>
       </c>
       <c r="I3">
-        <v>62.50000000000001</v>
+        <v>-5.658536585365853</v>
       </c>
       <c r="J3">
-        <v>62.50000000000001</v>
+        <v>-5.658536585365853</v>
       </c>
       <c r="K3">
-        <v>-0.983</v>
+        <v>1.73</v>
       </c>
       <c r="L3">
-        <v>22.34090909090909</v>
+        <v>10.54878048780488</v>
       </c>
       <c r="M3">
-        <v>1.2</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1709401709401709</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-1.220752797558494</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,82 +749,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>1.2</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>8.44</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
-        <v>1.202279202279202</v>
+        <v>0.6723404255319149</v>
       </c>
       <c r="W3">
-        <v>-0.0387007874015748</v>
+        <v>0.1168918918918919</v>
       </c>
       <c r="X3">
-        <v>0.2463191384115217</v>
+        <v>0.4266066974440045</v>
       </c>
       <c r="Y3">
-        <v>-0.2850199258130965</v>
+        <v>-0.3097148055521126</v>
       </c>
       <c r="Z3">
-        <v>-0.002321287259298338</v>
+        <v>0.01228832609021429</v>
       </c>
       <c r="AA3">
-        <v>-0.1450804537061461</v>
+        <v>-0.06953394275438333</v>
       </c>
       <c r="AB3">
-        <v>0.1532501894112694</v>
+        <v>0.2632683769096685</v>
       </c>
       <c r="AC3">
-        <v>-0.2983306431174154</v>
+        <v>-0.3328023196640518</v>
       </c>
       <c r="AD3">
-        <v>7.19</v>
+        <v>2.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.19</v>
+        <v>2.27</v>
       </c>
       <c r="AG3">
-        <v>-1.249999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.505981703026038</v>
+        <v>0.4913419913419914</v>
       </c>
       <c r="AI3">
-        <v>0.3299678751720973</v>
+        <v>0.13536076326774</v>
       </c>
       <c r="AJ3">
-        <v>-0.216637781629116</v>
+        <v>0.2269736842105263</v>
       </c>
       <c r="AK3">
-        <v>-0.09363295880149805</v>
+        <v>0.04542462146148782</v>
       </c>
       <c r="AL3">
-        <v>2.32</v>
+        <v>0.079</v>
       </c>
       <c r="AM3">
-        <v>2.32</v>
+        <v>-1.021</v>
       </c>
       <c r="AN3">
-        <v>-2.723484848484849</v>
+        <v>-3.802345058626466</v>
       </c>
       <c r="AO3">
-        <v>-1.185344827586207</v>
+        <v>-11.74683544303798</v>
       </c>
       <c r="AP3">
-        <v>0.4734848484848481</v>
+        <v>-1.155778894472362</v>
       </c>
       <c r="AQ3">
-        <v>-1.185344827586207</v>
+        <v>0.9089128305582761</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TraceSafe Inc. (CNSX:TSF)</t>
+          <t>ShiftCarbon Inc. (CNSX:SHFT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,31 +841,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.153968253968254</v>
+        <v>-0.5982721382289418</v>
       </c>
       <c r="H4">
-        <v>-0.3595238095238096</v>
+        <v>-0.8617710583153348</v>
       </c>
       <c r="I4">
-        <v>-0.5587918862222235</v>
+        <v>-0.7710583153347732</v>
       </c>
       <c r="J4">
-        <v>-0.5587918862222235</v>
+        <v>-0.7710583153347732</v>
       </c>
       <c r="K4">
-        <v>-3.66</v>
+        <v>-10.6</v>
       </c>
       <c r="L4">
-        <v>-0.2904761904761905</v>
+        <v>-2.289416846652268</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>2.3</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.7641196013289037</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.2169811320754717</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,76 +877,180 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.3</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>1.56</v>
+        <v>-0.034</v>
       </c>
       <c r="V4">
-        <v>0.088135593220339</v>
+        <v>-0.01129568106312293</v>
       </c>
       <c r="W4">
-        <v>-1.086053412462908</v>
+        <v>-3.569023569023569</v>
       </c>
       <c r="X4">
-        <v>0.1478767490812072</v>
+        <v>0.4250715120403666</v>
       </c>
       <c r="Y4">
-        <v>-1.233930161544115</v>
-      </c>
-      <c r="Z4">
-        <v>4.046387228251462</v>
-      </c>
-      <c r="AA4">
-        <v>-2.261088351660149</v>
+        <v>-3.994095081063935</v>
       </c>
       <c r="AB4">
-        <v>0.1461880968526111</v>
-      </c>
-      <c r="AC4">
-        <v>-2.407276448512761</v>
+        <v>0.3022563985284867</v>
       </c>
       <c r="AD4">
-        <v>0.348</v>
+        <v>2.88</v>
       </c>
       <c r="AE4">
-        <v>0.1388888320000831</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.4868888320000831</v>
+        <v>2.88</v>
       </c>
       <c r="AG4">
-        <v>-1.073111167999917</v>
+        <v>2.914</v>
       </c>
       <c r="AH4">
-        <v>0.02677141959230517</v>
+        <v>0.4889643463497453</v>
       </c>
       <c r="AI4">
-        <v>0.06988612043925854</v>
+        <v>4.96551724137931</v>
       </c>
       <c r="AJ4">
-        <v>-0.06454070745542058</v>
+        <v>0.4918973666441593</v>
       </c>
       <c r="AK4">
-        <v>-0.1984710988783097</v>
+        <v>4.745928338762216</v>
       </c>
       <c r="AL4">
-        <v>0.153</v>
+        <v>1.01</v>
       </c>
       <c r="AM4">
-        <v>0.153</v>
+        <v>1.01</v>
       </c>
       <c r="AN4">
-        <v>6.105263157894736</v>
+        <v>-0.7955801104972375</v>
       </c>
       <c r="AO4">
-        <v>-46.20915032679738</v>
+        <v>-3.534653465346535</v>
       </c>
       <c r="AP4">
-        <v>-18.82651171929679</v>
+        <v>-0.8049723756906076</v>
       </c>
       <c r="AQ4">
-        <v>-46.20915032679738</v>
+        <v>-3.534653465346535</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>British Virgin Islands</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Anemoi International Limited (LSE:AMOI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-3.467741935483871</v>
+      </c>
+      <c r="H5">
+        <v>-3.467741935483871</v>
+      </c>
+      <c r="I5">
+        <v>-8.629032258064516</v>
+      </c>
+      <c r="J5">
+        <v>-8.629032258064516</v>
+      </c>
+      <c r="K5">
+        <v>-1.13</v>
+      </c>
+      <c r="L5">
+        <v>-18.2258064516129</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>2.99</v>
+      </c>
+      <c r="V5">
+        <v>1.661111111111111</v>
+      </c>
+      <c r="W5">
+        <v>-1.027272727272727</v>
+      </c>
+      <c r="X5">
+        <v>0.2644821022749581</v>
+      </c>
+      <c r="Y5">
+        <v>-1.291754829547685</v>
+      </c>
+      <c r="AB5">
+        <v>0.2644821022749581</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-2.99</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>2.512605042016807</v>
+      </c>
+      <c r="AK5">
+        <v>-0.9060606060606061</v>
+      </c>
+      <c r="AL5">
+        <v>0.007</v>
+      </c>
+      <c r="AM5">
+        <v>0.007</v>
+      </c>
+      <c r="AO5">
+        <v>-76.42857142857143</v>
+      </c>
+      <c r="AQ5">
+        <v>-76.42857142857143</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_software_system_application.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,35 +587,32 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
-      <c r="E2">
-        <v>-0.0298</v>
-      </c>
       <c r="G2">
-        <v>-0.9586079077429984</v>
+        <v>-2.454391891891892</v>
       </c>
       <c r="H2">
-        <v>-1.209843492586491</v>
+        <v>-2.454391891891892</v>
       </c>
       <c r="I2">
-        <v>-1.036449752883031</v>
+        <v>-3.111486486486487</v>
       </c>
       <c r="J2">
-        <v>-1.036449752883031</v>
+        <v>-3.111486486486487</v>
       </c>
       <c r="K2">
-        <v>-10</v>
+        <v>-3.691</v>
       </c>
       <c r="L2">
-        <v>-2.059308072487644</v>
+        <v>-6.234797297297297</v>
       </c>
       <c r="M2">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.3212290502793296</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.23</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,73 +624,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>2.3</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4.536</v>
+        <v>3.16</v>
       </c>
       <c r="V2">
-        <v>0.6335195530726258</v>
+        <v>0.8381962864721486</v>
       </c>
       <c r="W2">
-        <v>-1.027272727272727</v>
+        <v>-0.1723953715963387</v>
       </c>
       <c r="X2">
-        <v>0.4250715120403666</v>
+        <v>0.1862750115431165</v>
       </c>
       <c r="Y2">
-        <v>-1.452344239313094</v>
+        <v>-0.3586703831394552</v>
       </c>
       <c r="Z2">
-        <v>0.3638543383785403</v>
+        <v>0.03543000778023819</v>
+      </c>
+      <c r="AA2">
+        <v>-0.3174786043449637</v>
       </c>
       <c r="AB2">
-        <v>0.2644821022749581</v>
+        <v>0.1477329865826166</v>
+      </c>
+      <c r="AC2">
+        <v>-0.4652115909275803</v>
       </c>
       <c r="AD2">
-        <v>5.15</v>
+        <v>1.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.15</v>
+        <v>1.99</v>
       </c>
       <c r="AG2">
-        <v>0.6139999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="AH2">
-        <v>0.4183590576766856</v>
+        <v>0.3454861111111111</v>
       </c>
       <c r="AI2">
-        <v>0.2178510998307953</v>
+        <v>0.09994977398292317</v>
       </c>
       <c r="AJ2">
-        <v>0.07898121944944686</v>
+        <v>-0.4500000000000001</v>
       </c>
       <c r="AK2">
-        <v>0.03213986599664991</v>
+        <v>-0.06985074626865674</v>
       </c>
       <c r="AL2">
-        <v>1.096</v>
+        <v>0.681</v>
       </c>
       <c r="AM2">
-        <v>-0.004000000000000004</v>
+        <v>0.678</v>
       </c>
       <c r="AN2">
-        <v>-1.221247332226701</v>
+        <v>-1.2905317769131</v>
       </c>
       <c r="AO2">
-        <v>-4.592153284671532</v>
+        <v>-2.704845814977973</v>
       </c>
       <c r="AP2">
-        <v>-0.1456011382499407</v>
+        <v>0.7587548638132298</v>
       </c>
       <c r="AQ2">
-        <v>1258.249999999999</v>
+        <v>-2.716814159292035</v>
       </c>
     </row>
     <row r="3">
@@ -712,26 +712,23 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
-      <c r="E3">
-        <v>-0.0298</v>
-      </c>
       <c r="G3">
-        <v>-10.18292682926829</v>
+        <v>-1.709333333333333</v>
       </c>
       <c r="H3">
-        <v>-10.18292682926829</v>
+        <v>-1.709333333333333</v>
       </c>
       <c r="I3">
-        <v>-5.658536585365853</v>
+        <v>-2.6</v>
       </c>
       <c r="J3">
-        <v>-5.658536585365853</v>
+        <v>-2.6</v>
       </c>
       <c r="K3">
-        <v>1.73</v>
+        <v>-2.77</v>
       </c>
       <c r="L3">
-        <v>10.54878048780488</v>
+        <v>-7.386666666666667</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,79 +746,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>0.78</v>
       </c>
       <c r="V3">
-        <v>0.6723404255319149</v>
+        <v>0.3347639484978541</v>
       </c>
       <c r="W3">
-        <v>0.1168918918918919</v>
+        <v>-0.1910344827586207</v>
       </c>
       <c r="X3">
-        <v>0.4266066974440045</v>
+        <v>0.2187010469937358</v>
       </c>
       <c r="Y3">
-        <v>-0.3097148055521126</v>
+        <v>-0.4097355297523565</v>
       </c>
       <c r="Z3">
-        <v>0.01228832609021429</v>
+        <v>0.02468729427254773</v>
       </c>
       <c r="AA3">
-        <v>-0.06953394275438333</v>
+        <v>-0.06418696510862409</v>
       </c>
       <c r="AB3">
-        <v>0.2632683769096685</v>
+        <v>0.1416169970727359</v>
       </c>
       <c r="AC3">
-        <v>-0.3328023196640518</v>
+        <v>-0.20580396218136</v>
       </c>
       <c r="AD3">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="AG3">
-        <v>0.6899999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AH3">
-        <v>0.4913419913419914</v>
+        <v>0.4606481481481481</v>
       </c>
       <c r="AI3">
-        <v>0.13536076326774</v>
+        <v>0.1402396053558844</v>
       </c>
       <c r="AJ3">
-        <v>0.2269736842105263</v>
+        <v>0.3418079096045197</v>
       </c>
       <c r="AK3">
-        <v>0.04542462146148782</v>
+        <v>0.09023117076808351</v>
       </c>
       <c r="AL3">
-        <v>0.079</v>
+        <v>0.681</v>
       </c>
       <c r="AM3">
-        <v>-1.021</v>
+        <v>0.681</v>
       </c>
       <c r="AN3">
-        <v>-3.802345058626466</v>
+        <v>-2.412121212121212</v>
       </c>
       <c r="AO3">
-        <v>-11.74683544303798</v>
+        <v>-1.431718061674009</v>
       </c>
       <c r="AP3">
-        <v>-1.155778894472362</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="AQ3">
-        <v>0.9089128305582761</v>
+        <v>-1.431718061674009</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ShiftCarbon Inc. (CNSX:SHFT)</t>
+          <t>Anemoi International Limited (LSE:AMOI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,31 +838,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.5982721382289418</v>
+        <v>-3.741935483870968</v>
       </c>
       <c r="H4">
-        <v>-0.8617710583153348</v>
+        <v>-3.741935483870968</v>
       </c>
       <c r="I4">
-        <v>-0.7710583153347732</v>
+        <v>-3.995391705069125</v>
       </c>
       <c r="J4">
-        <v>-0.7710583153347732</v>
+        <v>-3.995391705069125</v>
       </c>
       <c r="K4">
-        <v>-10.6</v>
+        <v>-0.921</v>
       </c>
       <c r="L4">
-        <v>-2.289416846652268</v>
+        <v>-4.244239631336406</v>
       </c>
       <c r="M4">
-        <v>2.3</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.7641196013289037</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.2169811320754717</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -877,180 +874,73 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.3</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>-0.034</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>-0.01129568106312293</v>
+        <v>1.652777777777778</v>
       </c>
       <c r="W4">
-        <v>-3.569023569023569</v>
+        <v>-0.1537562604340568</v>
       </c>
       <c r="X4">
-        <v>0.4250715120403666</v>
+        <v>0.1538489760924972</v>
       </c>
       <c r="Y4">
-        <v>-3.994095081063935</v>
+        <v>-0.307605236526554</v>
+      </c>
+      <c r="Z4">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AA4">
+        <v>-0.5707702435813033</v>
       </c>
       <c r="AB4">
-        <v>0.3022563985284867</v>
+        <v>0.1538489760924972</v>
+      </c>
+      <c r="AC4">
+        <v>-0.7246192196738006</v>
       </c>
       <c r="AD4">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.914</v>
+        <v>-2.38</v>
       </c>
       <c r="AH4">
-        <v>0.4889643463497453</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>4.96551724137931</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.4918973666441593</v>
+        <v>2.531914893617021</v>
       </c>
       <c r="AK4">
-        <v>4.745928338762216</v>
+        <v>-0.7125748502994012</v>
       </c>
       <c r="AL4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.01</v>
+        <v>-0.003</v>
       </c>
       <c r="AN4">
-        <v>-0.7955801104972375</v>
-      </c>
-      <c r="AO4">
-        <v>-3.534653465346535</v>
+        <v>-0</v>
       </c>
       <c r="AP4">
-        <v>-0.8049723756906076</v>
+        <v>3.319386331938633</v>
       </c>
       <c r="AQ4">
-        <v>-3.534653465346535</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>British Virgin Islands</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Anemoi International Limited (LSE:AMOI)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Software (System &amp; Application)</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>-3.467741935483871</v>
-      </c>
-      <c r="H5">
-        <v>-3.467741935483871</v>
-      </c>
-      <c r="I5">
-        <v>-8.629032258064516</v>
-      </c>
-      <c r="J5">
-        <v>-8.629032258064516</v>
-      </c>
-      <c r="K5">
-        <v>-1.13</v>
-      </c>
-      <c r="L5">
-        <v>-18.2258064516129</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2.99</v>
-      </c>
-      <c r="V5">
-        <v>1.661111111111111</v>
-      </c>
-      <c r="W5">
-        <v>-1.027272727272727</v>
-      </c>
-      <c r="X5">
-        <v>0.2644821022749581</v>
-      </c>
-      <c r="Y5">
-        <v>-1.291754829547685</v>
-      </c>
-      <c r="AB5">
-        <v>0.2644821022749581</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>-2.99</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>2.512605042016807</v>
-      </c>
-      <c r="AK5">
-        <v>-0.9060606060606061</v>
-      </c>
-      <c r="AL5">
-        <v>0.007</v>
-      </c>
-      <c r="AM5">
-        <v>0.007</v>
-      </c>
-      <c r="AO5">
-        <v>-76.42857142857143</v>
-      </c>
-      <c r="AQ5">
-        <v>-76.42857142857143</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
